--- a/manya-react/public/content/math/math_p7_question_bank.xlsx
+++ b/manya-react/public/content/math/math_p7_question_bank.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manya_app\content\math\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manya_app\manya-react\public\content\math\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7305" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7305"/>
   </bookViews>
   <sheets>
     <sheet name="RAW" sheetId="1" r:id="rId1"/>
@@ -8811,16 +8811,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:V342"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="69.140625" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" customWidth="1"/>
     <col min="16" max="16" width="21.42578125" customWidth="1"/>
@@ -30439,6 +30440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30446,6 +30448,7 @@
     <col min="3" max="3" width="25.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.42578125" customWidth="1"/>
     <col min="9" max="9" width="53.85546875" customWidth="1"/>
+    <col min="16" max="16" width="255.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="46.28515625" customWidth="1"/>
     <col min="19" max="19" width="38.42578125" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" customWidth="1"/>
